--- a/output/RESULT.xlsx
+++ b/output/RESULT.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BABY</t>
+          <t>ПАРФЮМИРОВАННЫЙ BABY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MIDNIGHT</t>
+          <t>ПАРФЮМИРОВАННЫЙ MIDNIGHT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VELVET</t>
+          <t>ПАРФЮМИРОВАННЫЙ VELVET</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FLORAL MIST</t>
+          <t>ПАРФЮМИРОВАННЫЙ FLORAL MIST</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SWEET TROPIC</t>
+          <t>ПАРФЮМИРОВАННЫЙ SWEET TROPIC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DREAM</t>
+          <t>ПАРФЮМИРОВАННЫЙ DREAM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BLACK</t>
+          <t>ПАРФЮМИРОВАННЫЙ BLACK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SHAFRAN</t>
+          <t>ПАРФЮМИРОВАННЫЙ SHAFRAN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -778,9 +778,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SKU-032</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Saffran 1 л</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -802,7 +812,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>() 2 ПИОН</t>
+          <t>ПАРФЮМИРОВАННЫЙ () 2 ПИОН</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -834,7 +844,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>() 2 ГОРНЫЙ БРИЗ</t>
+          <t>ПАРФЮМИРОВАННЫ() 2 ГОРНЫЙ БРИЗ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -866,7 +876,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>() 2 АРОМАТ ЦВЕТОВ</t>
+          <t>ПАРФЮМИРОВАННЫЙ() 2 АРОМАТ ЦВЕТОВ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -898,7 +908,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ВАНИЛЬ () 2</t>
+          <t>ПАРФЮМИРОВАННЫЙ ВАНИЛЬ () 2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -930,7 +940,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ЛАВАНДА () 2</t>
+          <t>ПАРФЮМИРОВАННЫЙ ЛАВАНДА () 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -962,7 +972,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>РОЗА () 2</t>
+          <t>ПАРФЮМИРОВАННЫЙ РОЗА () 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -994,7 +1004,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>РОМАШКА PAPATYA 2</t>
+          <t>ПАРФЮМИРОВАННЫЙ РОМАШКА PAPATYA 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1002,9 +1012,19 @@
           <t>7 л</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKU-040</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Papatya 1,44 л</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1046,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ПОЛНОЧЬ MIDNIGHT 2</t>
+          <t>ПАРФЮМИРОВАННЫЙ ПОЛНОЧЬ MIDNIGHT 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1034,9 +1054,19 @@
           <t>7 л</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKU-026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Midnight 1 л</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1088,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>АРОМАТ СТРАСТИ DAHLIA 2</t>
+          <t>ПАРФЮМИРОВАННЫЙ АРОМАТ СТРАСТИ DAHLIA 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1090,7 +1120,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ТАИНСТВЕННЫЙ ЛОТОС LOTOS</t>
+          <t>ПАРФЮМИРОВАННЫЙ ТАИНСТВЕННЫЙ ЛОТОС LOTOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1117,7 +1147,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ЦВЕТОЧНЫЙ ТУМАН FLORIAL 2 7</t>
+          <t>ПАРФЮМИРОВАННЫЙ ЦВЕТОЧНЫЙ ТУМАН FLORIAL 2 7</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1144,7 +1174,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>МАНГО MANGO 2</t>
+          <t>ПАРФЮМИРОВАННЫЙ МАНГО MANGO 2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1176,7 +1206,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ДЛЯ ТЕМНОГО БЕЛЬЯ 2</t>
+          <t>ПАРФЮМИРОВАННЫЙ ДЛЯ ТЕМНОГО БЕЛЬЯ 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1238,9 +1268,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKU-009</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Шампунь men GILAR Keratin Extracts 400 мл</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1314,9 +1354,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SKU-013</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Шампунь sport GILAR Blue 400 мл</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1346,9 +1396,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SKU-012</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Шампунь sport GILAR Black 400 мл</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1607,9 +1667,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SKU-262</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Pomegranate 1 л</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1634,9 +1704,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SKU-262</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Pomegranate 1 л</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1661,9 +1741,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SKU-028</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Floral Mist 1 л</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1688,9 +1778,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SKU-026</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Midnight 1 л</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1715,9 +1815,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SKU-029</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Sweet Tropic 1 л</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1742,9 +1852,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SKU-029</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Sweet Tropic 1 л</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1769,9 +1889,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SKU-027</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Velvet 1 л</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1796,9 +1926,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SKU-262</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Pomegranate 1 л</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1985,9 +2125,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SKU-270</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Orange 2 л</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2012,9 +2162,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SKU-271</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Lemon 2 л</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2039,9 +2199,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SKU-272</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Wild Berries 2 л</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2066,9 +2236,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SKU-273</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Apple 2 л</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2093,9 +2273,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SKU-274</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Ginger 2 л</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2120,9 +2310,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SKU-275</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Passion Fruit 2 л</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2147,9 +2347,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SKU-276</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Pomegranate 2 л</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2174,9 +2384,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SKU-277</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Strawberry 2 л</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2201,9 +2421,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SKU-278</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Mango 2 л</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2390,9 +2620,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SKU-073</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Love Is 5 л</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2417,9 +2657,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SKU-073</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Love Is 5 л</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2636,9 +2886,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SKU-114</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Passion Fruit 500 мл</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2663,9 +2923,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SKU-115</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Chocolate 500 мл</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2690,9 +2960,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SKU-116</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Mango 500 мл</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2717,9 +2997,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SKU-117</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Wild Berries 500 мл</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2744,9 +3034,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SKU-118</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Coconut 500 мл</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2771,9 +3071,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SKU-119</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Oatmeal 500 мл</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2798,9 +3108,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SKU-120</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Oriental 500 мл</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2825,9 +3145,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SKU-121</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Pine Forest 500 мл</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2852,9 +3182,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SKU-122</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Cherry 500 мл</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2884,9 +3224,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>SKU-014</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Almond 600 мл</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2916,9 +3266,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>SKU-015</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Aloe Vera 600 мл</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2948,9 +3308,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>SKU-016</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Garlic 600 мл</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -2980,9 +3350,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>SKU-017</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Keratin 600 мл</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -3012,9 +3392,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SKU-018</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Mint 600 мл</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -3044,9 +3434,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>SKU-019</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Nettle 600 мл</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -4843,9 +5243,19 @@
           <t>BOSSFIX</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>SKU-082</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>ЖМС BOSSFIX Baby 1 л</t>
+        </is>
+      </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -4860,9 +5270,19 @@
           <t>BOSSFIX</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>SKU-082</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>ЖМС BOSSFIX Baby 1 л</t>
+        </is>
+      </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -4884,7 +5304,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>MAGINA АРАБСКИЙ ПАРФЮМ 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ MAGINA АРАБСКИЙ ПАРФЮМ 1</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -4916,7 +5336,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VELVET 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ VELVET 1</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -4924,9 +5344,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>SKU-027</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Velvet 1 л</t>
+        </is>
+      </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -4948,7 +5378,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ЛОТОС 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ ЛОТОС 1</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -4980,7 +5410,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>МАНГО 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ МАНГО 1</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5012,7 +5442,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>DREAM 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ DREAM 1</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5020,9 +5450,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>SKU-030</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Dream 1 л</t>
+        </is>
+      </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5484,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>MIDNIGHT 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ MIDNIGHT 1</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5052,9 +5492,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>SKU-026</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Midnight 1 л</t>
+        </is>
+      </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5526,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>TUTKULU DOHLIA СТРАСТИ 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ TUTKULU DOHLIA СТРАСТИ 1</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5084,9 +5534,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>SKU-039</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Tutkulu Dahlia 1,44 л</t>
+        </is>
+      </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5568,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PAPATYE РОМАШКА 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ PAPATYE РОМАШКА 1</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -5116,9 +5576,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>SKU-040</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Papatya 1,44 л</t>
+        </is>
+      </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5610,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>FLORAL MIST 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ FLORAL MIST 1</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -5148,9 +5618,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>SKU-028</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Floral Mist 1 л</t>
+        </is>
+      </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5652,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>PASSION FRUIT МАРАКУЙЯ 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ PASSION FRUIT МАРАКУЙЯ 1</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5180,9 +5660,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>SKU-042</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Passion Fruit 1,44 л</t>
+        </is>
+      </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5694,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ORCHIDE ОРХИДЕЯ 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ ORCHIDE ОРХИДЕЯ 1</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -5212,9 +5702,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>SKU-043</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Orchide 1,44 л</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5736,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>SAFFRAN ШАФРАН 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ SAFFRAN ШАФРАН 1</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5244,9 +5744,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>SKU-032</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Saffran 1 л</t>
+        </is>
+      </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5778,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>SHAIK ШЕЙХ 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ SHAIK ШЕЙХ 1</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5276,9 +5786,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>SKU-045</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Shaik 1,44 л</t>
+        </is>
+      </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5820,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>JASMIN ЖАСМИН 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ JASMIN ЖАСМИН 1</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5308,9 +5828,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>SKU-046</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Jasmin 1,44 л</t>
+        </is>
+      </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5332,12 +5862,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ROMANTIK ROSE РОМАНТИЧНАЯ РОЗА 1 44</t>
+          <t>ПАРФЮМИРОВАННЫЙ ROMANTIK ROSE РОМАНТИЧНАЯ РОЗА 1 44</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>SKU-047</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Romantik Rose 1,44 л</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5899,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>SWEET TROPIC 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ SWEET TROPIC 1</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -5367,9 +5907,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>SKU-029</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Sweet Tropic 1 л</t>
+        </is>
+      </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5941,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ROSE РОЗА 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ ROSE РОЗА 1</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -5423,7 +5973,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>BOTANIC СЕНТЯБРЬСКОЕ СОЛНЦЕ 1</t>
+          <t>BOTANIC ПАРФЮМИРОВАННЫЙ СЕНТЯБРЬСКОЕ СОЛНЦЕ 1</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5455,7 +6005,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>BOTANIC ДОЖДЛИВЫЙ АПРЕЛЬ 1</t>
+          <t>BOTANIC ПАРФЮМИРОВАННЫЙ ДОЖДЛИВЫЙ АПРЕЛЬ 1</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -5487,7 +6037,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>BLACKBERRY ЕЖЕВИКА 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ BLACKBERRY ЕЖЕВИКА 1</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -5495,9 +6045,19 @@
           <t>44 л</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>SKU-052</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Blackberry 1,44 л</t>
+        </is>
+      </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5519,7 +6079,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>BABY ДЕТСКИЙ 1</t>
+          <t>ПАРФЮМИРОВАННЫЙ BABY ДЕТСКИЙ 1</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -5586,9 +6146,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>SKU-073</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Love Is 5 л</t>
+        </is>
+      </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5613,9 +6183,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>SKU-072</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Maiden Tower 5 л</t>
+        </is>
+      </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5640,9 +6220,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>SKU-073</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Love Is 5 л</t>
+        </is>
+      </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5667,9 +6257,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>SKU-072</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Maiden Tower 5 л</t>
+        </is>
+      </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5694,9 +6294,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>SKU-073</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Love Is 5 л</t>
+        </is>
+      </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5721,9 +6331,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>SKU-072</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Maiden Tower 5 л</t>
+        </is>
+      </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5748,9 +6368,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>SKU-069</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Frezya 5 л</t>
+        </is>
+      </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5775,9 +6405,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>SKU-073</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Love Is 5 л</t>
+        </is>
+      </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5802,9 +6442,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>SKU-073</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Love Is 5 л</t>
+        </is>
+      </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5829,9 +6479,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>SKU-068</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Ask 5 л</t>
+        </is>
+      </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5856,9 +6516,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>SKU-072</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Maiden Tower 5 л</t>
+        </is>
+      </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5883,9 +6553,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>SKU-094</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Midnight 3 л</t>
+        </is>
+      </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5910,9 +6590,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>SKU-095</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Dream 3 л</t>
+        </is>
+      </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5937,9 +6627,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>SKU-096</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Velvet 3 л</t>
+        </is>
+      </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -5991,9 +6691,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>SKU-098</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Black 3 л</t>
+        </is>
+      </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6018,9 +6728,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>SKU-099</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Color 3 л</t>
+        </is>
+      </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6045,9 +6765,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>SKU-100</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>ЖМС SVO White 3 л</t>
+        </is>
+      </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6158,9 +6888,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>SKU-020</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Шампунь органический GILAR Argan Oil 500 мл</t>
+        </is>
+      </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6190,9 +6930,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>SKU-021</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Шампунь органический GILAR Coffee 500 мл</t>
+        </is>
+      </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6222,9 +6972,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>SKU-022</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Шампунь органический GILAR Ginger 500 мл</t>
+        </is>
+      </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6254,9 +7014,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>SKU-023</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Шампунь органический GILAR Lavender 500 мл</t>
+        </is>
+      </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6286,9 +7056,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>SKU-024</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Шампунь органический GILAR Ginseng 500 мл</t>
+        </is>
+      </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6313,9 +7093,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>SKU-261</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Orange 1 л</t>
+        </is>
+      </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6340,9 +7130,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>SKU-262</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Pomegranate 1 л</t>
+        </is>
+      </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6367,9 +7167,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>SKU-263</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Wild Berries 1 л</t>
+        </is>
+      </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6394,9 +7204,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>SKU-264</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Ginger 1 л</t>
+        </is>
+      </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6421,9 +7241,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>SKU-265</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Strawberry 1 л</t>
+        </is>
+      </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6448,9 +7278,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>SKU-266</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Lemon 1 л</t>
+        </is>
+      </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6475,9 +7315,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>SKU-267</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Mango 1 л</t>
+        </is>
+      </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6502,9 +7352,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>SKU-268</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Passion 1 л</t>
+        </is>
+      </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6529,9 +7389,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SKU-269</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Apple 1 л</t>
+        </is>
+      </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6553,7 +7423,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ASK ЛЮБОВЬ</t>
+          <t>ПАРФЮМИРОВАННЫЙ ASK ЛЮБОВЬ</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -6561,9 +7431,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>SKU-068</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Ask 5 л</t>
+        </is>
+      </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6585,7 +7465,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>FREZYA ИРИС</t>
+          <t>ПАРФЮМИРОВАННЫЙ FREZYA ИРИС</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -6593,9 +7473,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>SKU-069</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Frezya 5 л</t>
+        </is>
+      </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6617,7 +7507,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>GUL РОЗА</t>
+          <t>ПАРФЮМИРОВАННЫЙ GUL РОЗА</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -6625,9 +7515,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>SKU-070</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Gul 5 л</t>
+        </is>
+      </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6649,7 +7549,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>HUZUR УСПОКАИВАЮЩИЙ</t>
+          <t>ПАРФЮМИРОВАННЫЙ HUZUR УСПОКАИВАЮЩИЙ</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -6657,9 +7557,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>SKU-071</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Huzur 5 л</t>
+        </is>
+      </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6681,7 +7591,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>MAIDEN TOWER ОРХИДЕЯ</t>
+          <t>ПАРФЮМИРОВАННЫЙ MAIDEN TOWER ОРХИДЕЯ</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -6689,9 +7599,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>SKU-072</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Maiden Tower 5 л</t>
+        </is>
+      </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6713,7 +7633,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LOVE IS ЦВЕТОЧНЫЙ</t>
+          <t>ПАРФЮМИРОВАННЫЙ LOVE IS ЦВЕТОЧНЫЙ</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -6721,9 +7641,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>SKU-073</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Love Is 5 л</t>
+        </is>
+      </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -6838,9 +7768,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>SKU-020</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Шампунь органический GILAR Argan Oil 500 мл</t>
+        </is>
+      </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -7235,9 +8175,19 @@
           <t>7 л</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>SKU-039</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Tutkulu Dahlia 1,44 л</t>
+        </is>
+      </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -7267,9 +8217,19 @@
           <t>7 л</t>
         </is>
       </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>SKU-059</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Lavender 2,7 л</t>
+        </is>
+      </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -7294,9 +8254,19 @@
           <t>РОМАНТИЧЕСКИЙ АРОМАТ ROMANTIK GUL 3В1</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>SKU-047</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Romantik Rose 1,44 л</t>
+        </is>
+      </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -7326,9 +8296,19 @@
           <t>7 л</t>
         </is>
       </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>SKU-028</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Floral Mist 1 л</t>
+        </is>
+      </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -7358,9 +8338,19 @@
           <t>7 л</t>
         </is>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>SKU-067</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Black Gel 2,7 л</t>
+        </is>
+      </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -7390,9 +8380,19 @@
           <t>7 л</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>SKU-026</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Midnight 1 л</t>
+        </is>
+      </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -7407,9 +8407,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>SKU-025</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Baby 1 л</t>
+        </is>
+      </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -7424,9 +8434,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>SKU-025</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Baby 1 л</t>
+        </is>
+      </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>

--- a/output/RESULT.xlsx
+++ b/output/RESULT.xlsx
@@ -476,12 +476,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ BABY</t>
+          <t>BABY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,12 +518,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ MIDNIGHT</t>
+          <t>MIDNIGHT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ VELVET</t>
+          <t>VELVET</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ FLORAL MIST</t>
+          <t>FLORAL MIST</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ SWEET TROPIC</t>
+          <t>SWEET TROPIC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ DREAM</t>
+          <t>DREAM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ BLACK</t>
+          <t>BLACK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -770,27 +770,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ SHAFRAN</t>
+          <t>SHAFRAN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SKU-032</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Saffran 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -812,12 +802,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ () 2 ПИОН</t>
+          <t>() 2 ПИОН</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -844,12 +834,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫ() 2 ГОРНЫЙ БРИЗ</t>
+          <t>() 2 ГОРНЫЙ БРИЗ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -876,12 +866,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ() 2 АРОМАТ ЦВЕТОВ</t>
+          <t>() 2 АРОМАТ ЦВЕТОВ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -908,12 +898,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ ВАНИЛЬ () 2</t>
+          <t>ВАНИЛЬ () 2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -940,12 +930,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ ЛАВАНДА () 2</t>
+          <t>ЛАВАНДА () 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -972,12 +962,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ РОЗА () 2</t>
+          <t>РОЗА () 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1004,27 +994,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ РОМАШКА PAPATYA 2</t>
+          <t>РОМАШКА PAPATYA 2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7 л</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKU-040</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Papatya 1,44 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1026,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ ПОЛНОЧЬ MIDNIGHT 2</t>
+          <t>ПОЛНОЧЬ MIDNIGHT 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7 л</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKU-026</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Midnight 1 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1058,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ АРОМАТ СТРАСТИ DAHLIA 2</t>
+          <t>АРОМАТ СТРАСТИ DAHLIA 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1120,7 +1090,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ ТАИНСТВЕННЫЙ ЛОТОС LOTOS</t>
+          <t>ТАИНСТВЕННЫЙ ЛОТОС LOTOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1147,7 +1117,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ ЦВЕТОЧНЫЙ ТУМАН FLORIAL 2 7</t>
+          <t>ЦВЕТОЧНЫЙ ТУМАН FLORIAL 2 7</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1174,12 +1144,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ МАНГО MANGO 2</t>
+          <t>МАНГО MANGO 2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1206,12 +1176,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ ДЛЯ ТЕМНОГО БЕЛЬЯ 2</t>
+          <t>+ ГЕЛЬ ДЛЯ ТЕМНОГО БЕЛЬЯ 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1226,14 +1196,9 @@
           <t>Шампунь мужской с лаймом GILA’R MEN Lemon Oil 400 мл</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1248,11 +1213,6 @@
           <t>Шампунь мужской с кератином GILAR MEN Keratin Extracts 400 мл</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -1260,27 +1220,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MEN KERATIN EXTRACTS</t>
+          <t>МУЖСКОЙ С КЕРАТИНОМ MEN KERATIN EXTRACTS</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>400 мл</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKU-009</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Шампунь men GILAR Keratin Extracts 400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1290,14 +1240,9 @@
           <t>Шампунь мужской  с аргановым маслом GILA’R MEN ARGAN Oil 400 мл</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1312,14 +1257,9 @@
           <t>Шампунь мужской с оливковым маслом GILA’R MEN Olive Oil 400 мл</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1334,11 +1274,6 @@
           <t>Шампунь для мужчин GILAR SPORT BLUE (восст)  400 мл</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -1346,27 +1281,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SPORT BLUE (ВОССТ)</t>
+          <t>ДЛЯ МУЖЧИН SPORT BLUE (ВОССТ)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>400 мл</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>SKU-013</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Шампунь sport GILAR Blue 400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1376,11 +1301,6 @@
           <t>Шампунь для мужчин GILAR SPORT BLACK (от перх) 400 мл</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -1388,27 +1308,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SPORT BLACK (ОТ ПЕРХ)</t>
+          <t>ДЛЯ МУЖЧИН SPORT BLACK (ОТ ПЕРХ)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>400 мл</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>SKU-012</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Шампунь sport GILAR Black 400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1418,14 +1328,9 @@
           <t>Шампунь  женский с ароматом крокуса GILA’R women Intense 400 мл</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1440,14 +1345,9 @@
           <t>Шампунь женский с ароматом розы GILA’R women lovely moments 400 мл</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1462,14 +1362,9 @@
           <t>Шампунь женский с ароматом пиона GILA’R women Charm 400 мл</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1496,27 +1391,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AVOCADO</t>
+          <t>С АРОМАТОМ АВОКАДО AVOCADO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>400 мл</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>SKU-002</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Гель для душа GILAR Avocado 400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1538,27 +1423,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CHERRY</t>
+          <t>С АРОМАТОМ ВИШНИ CHERRY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>400 мл</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>SKU-001</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Гель для душа GILAR Cherry 400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1580,27 +1455,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BLACKBERRY</t>
+          <t>С АРОМАТОМ ЕЖЕВИКИ BLACKBERRY</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>400 мл</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>SKU-004</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Гель для душа GILAR Blackberry 400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1622,27 +1487,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MANGO</t>
+          <t>С АРОМАТОМ МАНГО MANGO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>400 мл</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>SKU-003</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Гель для душа GILAR Mango 400 мл</t>
+          <t>400 МЛ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1659,27 +1514,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ БЕЛОГО БЕЛЬЯ</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ БЕЛОГО БЕЛЬЯ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>SKU-262</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Pomegranate 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1696,27 +1541,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ DREAM</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ DREAM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>SKU-262</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Pomegranate 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1733,27 +1568,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ FLORAL</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ FLORAL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>SKU-028</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Floral Mist 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1770,27 +1595,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ MIDNIGHT</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ MIDNIGHT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>SKU-026</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Midnight 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1807,27 +1622,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ SPRING</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ SPRING</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>SKU-029</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Sweet Tropic 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1844,27 +1649,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ SWEET TROPIC</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ SWEET TROPIC</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>SKU-029</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Sweet Tropic 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1881,27 +1676,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ VELVET</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ VELVET</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>SKU-027</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Velvet 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1918,27 +1703,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЧЕРНОГО БЕЛЬЯ</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЧЕРНОГО БЕЛЬЯ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>SKU-262</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Pomegranate 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1730,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ДЛЯ ДЕТСКОГО БЕЛЬЯ</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ДЛЯ ДЕТСКОГО БЕЛЬЯ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1982,12 +1757,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>АПЕЛЬСИН</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ АПЕЛЬСИН</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>750 мл</t>
+          <t>750 МЛ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2009,12 +1784,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ГРЕЙПФРУТ</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ ГРЕЙПФРУТ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>750 мл</t>
+          <t>750 МЛ</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2036,12 +1811,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ЛИМОН</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ ЛИМОН</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>750 мл</t>
+          <t>750 МЛ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2063,12 +1838,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ЯБЛОКО</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ ЯБЛОКО</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>750 мл</t>
+          <t>750 МЛ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2090,12 +1865,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>МАНГО</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ МАНГО</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>750 мл</t>
+          <t>750 МЛ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2117,27 +1892,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ORANGE АПЕЛЬСИН</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ ORANGE АПЕЛЬСИН</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2 л</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>SKU-270</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Orange 2 л</t>
+          <t>2 Л</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2154,27 +1919,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LEMON ЛИМОН</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ LEMON ЛИМОН</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2 л</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>SKU-271</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Lemon 2 л</t>
+          <t>2 Л</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2191,27 +1946,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>WILDBERRIES ЛЕСНЫЕ ЯГОДЫ</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ WILDBERRIES ЛЕСНЫЕ ЯГОДЫ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2 л</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>SKU-272</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Wild Berries 2 л</t>
+          <t>2 Л</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2228,27 +1973,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>APPLE ЯБЛОКО</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ APPLE ЯБЛОКО</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2 л</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>SKU-273</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Apple 2 л</t>
+          <t>2 Л</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2265,27 +2000,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>GINGER ИМБИРЬ</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ GINGER ИМБИРЬ</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2 л</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>SKU-274</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Ginger 2 л</t>
+          <t>2 Л</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2302,27 +2027,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PASSION FRUIT МАРАКУЙЯ</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ PASSION FRUIT МАРАКУЙЯ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2 л</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>SKU-275</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Passion Fruit 2 л</t>
+          <t>2 Л</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2339,27 +2054,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>POMEGRANATE ГРАНАТ</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ POMEGRANATE ГРАНАТ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2 л</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>SKU-276</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Pomegranate 2 л</t>
+          <t>2 Л</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2376,27 +2081,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>STRAWBERRY КЛУБНИКА</t>
+          <t>МОЮЩЕЕ СРЕСТВО ДЛЯ МЫТЬЯ ПОСУДЫ STRAWBERRY КЛУБНИКА</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2 л</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>SKU-277</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Strawberry 2 л</t>
+          <t>2 Л</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2413,27 +2108,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MANGO МАНГО</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ MANGO МАНГО</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2 л</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>SKU-278</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Mango 2 л</t>
+          <t>2 Л</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2135,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>(АПЕЛЬСИН)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ (АПЕЛЬСИН)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4 л</t>
+          <t>4 Л</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2477,12 +2162,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(ГРЕЙПФРУТ)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ (ГРЕЙПФРУТ)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>4 л</t>
+          <t>4 Л</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2504,12 +2189,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>(ЛИМОН)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ (ЛИМОН)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>4 л</t>
+          <t>4 Л</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2531,12 +2216,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>(ЯБЛОКО)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ (ЯБЛОКО)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>4 л</t>
+          <t>4 Л</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2558,12 +2243,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>()</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОЛА ()</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2585,12 +2270,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>()</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОЛА ()</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2612,27 +2297,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2 ()</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОЛА 2 ()</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>SKU-073</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Love Is 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2649,27 +2324,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2 ()</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОЛА 2 ()</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>SKU-073</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Love Is 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2435,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>С АРОМАТОМ ЛАВАНДЫ</t>
+          <t>ЖИДКОЕ МЫЛО С АРОМАТОМ ЛАВАНДЫ</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -2797,12 +2462,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>С АРОМАТОМ ОКЕАНА</t>
+          <t>ЖИДКОЕ МЫЛО С АРОМАТОМ ОКЕАНА</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -2824,12 +2489,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>С АРОМАТОМ РОЗЫ</t>
+          <t>ЖИДКОЕ МЫЛО С АРОМАТОМ РОЗЫ</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2851,12 +2516,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>С ОЛИВКОВЫМ АРОМАТОМ</t>
+          <t>ЖИДКОЕ МЫЛО С ОЛИВКОВЫМ АРОМАТОМ</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -2878,27 +2543,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>МАРАКУЙЯ PASSION FRUTT</t>
+          <t>ЖИДКОЕ МЫЛО МАРАКУЙЯ PASSION FRUTT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>SKU-114</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Жидкое мыло SVO Passion Fruit 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2915,27 +2570,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ШОКОЛАД COCOLADE</t>
+          <t>ЖИДКОЕ МЫЛО ШОКОЛАД COCOLADE</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>SKU-115</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Жидкое мыло SVO Chocolate 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2952,27 +2597,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>МАНГО MANGO</t>
+          <t>ЖИДКОЕ МЫЛО МАНГО MANGO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>SKU-116</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Жидкое мыло SVO Mango 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -2989,27 +2624,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ЛЕСНЫЕ ЯГОДЫ WILDBERES</t>
+          <t>ЖИДКОЕ МЫЛО ЛЕСНЫЕ ЯГОДЫ WILDBERES</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>SKU-117</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Жидкое мыло SVO Wild Berries 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3026,27 +2651,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>COCONUT С АРОМАТОМ КОКОСА</t>
+          <t>ЖИДКОЕ КРЕМ-МЫЛО COCONUT С АРОМАТОМ КОКОСА</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>SKU-118</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Крем-мыло GILAR Coconut 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3063,27 +2678,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OATMEAL С АРОМАТОМ ОВСЯНОГО МОЛОЧКА</t>
+          <t>ЖИДКОЕ КРЕМ-МЫЛО OATMEAL С АРОМАТОМ ОВСЯНОГО МОЛОЧКА</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>SKU-119</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Крем-мыло GILAR Oatmeal 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3100,27 +2705,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ORIENTAL С ВОСТОЧНЫМ АРОМАТОМ</t>
+          <t>ЖИДКОЕ КРЕМ-МЫЛО ORIENTAL С ВОСТОЧНЫМ АРОМАТОМ</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>SKU-120</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Крем-мыло GILAR Oriental 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3137,27 +2732,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PINE FOREST С АРОМАТОМ СОСНОВОГО ЛЕСА</t>
+          <t>ЖИДКОЕ КРЕМ-МЫЛО PINE FOREST С АРОМАТОМ СОСНОВОГО ЛЕСА</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>SKU-121</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Крем-мыло GILAR Pine Forest 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3174,27 +2759,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>СHERRY С АРОМАТОМ ВИШНИ</t>
+          <t>ЖИДКОЕ КРЕМ-МЫЛО СHERRY С АРОМАТОМ ВИШНИ</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>SKU-122</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Крем-мыло GILAR Cherry 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3204,11 +2779,6 @@
           <t>Шампунь для волос GILAR ALMOND (миндаль + мед) 600 мл.</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C87" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -3216,27 +2786,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ALMOND (МИНДАЛЬ + МЕД) .</t>
+          <t>ДЛЯ ВОЛОС ALMOND (МИНДАЛЬ + МЕД) .</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>600 мл</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>SKU-014</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Шампунь GILAR Almond 600 мл</t>
+          <t>600 МЛ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3246,11 +2806,6 @@
           <t>Шампунь для волос GILAR ALOEVERA  (алоэ вера + хризантема) 600 мл.</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C88" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -3258,27 +2813,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ALOEVERA (АЛОЭ ВЕРА + ХРИЗАНТЕМА) .</t>
+          <t>ДЛЯ ВОЛОС ALOEVERA (АЛОЭ ВЕРА + ХРИЗАНТЕМА) .</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>600 мл</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>SKU-015</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Шампунь GILAR Aloe Vera 600 мл</t>
+          <t>600 МЛ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3288,11 +2833,6 @@
           <t>Шампунь для волос GILAR GARLIC (чеснок) 600 мл.</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C89" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -3300,27 +2840,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>GARLIC (ЧЕСНОК) .</t>
+          <t>ДЛЯ ВОЛОС GARLIC (ЧЕСНОК) .</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>600 мл</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>SKU-016</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Шампунь GILAR Garlic 600 мл</t>
+          <t>600 МЛ</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3330,11 +2860,6 @@
           <t>Шампунь для волос GILAR KERATIN (кератин + зеленый чай) 600 мл.</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C90" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -3342,27 +2867,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KERATIN (КЕРАТИН + ЗЕЛЕНЫЙ ЧАЙ) .</t>
+          <t>ДЛЯ ВОЛОС KERATIN (КЕРАТИН + ЗЕЛЕНЫЙ ЧАЙ) .</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>600 мл</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>SKU-017</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Шампунь GILAR Keratin 600 мл</t>
+          <t>600 МЛ</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3372,11 +2887,6 @@
           <t>Шампунь для волос GILAR MINT (ментол) 600 мл.</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C91" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -3384,27 +2894,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MINT (МЕНТОЛ) .</t>
+          <t>ДЛЯ ВОЛОС MINT (МЕНТОЛ) .</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>600 мл</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>SKU-018</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Шампунь GILAR Mint 600 мл</t>
+          <t>600 МЛ</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3414,11 +2914,6 @@
           <t>Шампунь для волос GILAR NETTLE (крапива) 600 мл.</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C92" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -3426,27 +2921,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NETTLE (КРАПИВА) .</t>
+          <t>ДЛЯ ВОЛОС NETTLE (КРАПИВА) .</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>600 мл</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>SKU-019</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Шампунь GILAR Nettle 600 мл</t>
+          <t>600 МЛ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -3463,7 +2948,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ДЛЯ БЕЛОГО БЕЛЬЯ 750 Г</t>
+          <t>КИСЛОРОДНЫЙ ОТБЕЛИВАТЕЛЬ-ПЯТНОВЫВОДИТЕЛЬ ДЛЯ БЕЛОГО БЕЛЬЯ 750 Г</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3485,7 +2970,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ДЛЯ ЦВЕТНОГО БЕЛЬЯ 750 Г</t>
+          <t>КИСЛОРОДНЫЙ ОТБЕЛИВАТЕЛЬ-ПЯТНОВЫВОДИТЕЛЬ ДЛЯ ЦВЕТНОГО БЕЛЬЯ 750 Г</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3507,7 +2992,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ВЕСЕННИЙ БРИЗ ЦВЕТ&amp;БЕЛОЕ 400 Г</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК АВТОМАТ ВЕСЕННИЙ БРИЗ ЦВЕТ&amp;БЕЛОЕ 400 Г</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3529,7 +3014,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>DAG ESINTISI ГОРНЫЙ БРИЗ 400 Г</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК АВТОМАТ DAG ESINTISI ГОРНЫЙ БРИЗ 400 Г</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3551,7 +3036,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ДЛЯ ДЕТСКОГО БЕЛЬЯ 400 Г</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК АВТОМАТ ДЛЯ ДЕТСКОГО БЕЛЬЯ 400 Г</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3573,7 +3058,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LAVANTA ЛАВАНДА COLOR&amp;WHITE 400 Г</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК АВТОМАТ LAVANTA ЛАВАНДА COLOR&amp;WHITE 400 Г</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3595,7 +3080,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>COLOR ДЛЯ ЦВЕТНОГО БЕЛЬЯ 400 Г</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК АВТОМАТ COLOR ДЛЯ ЦВЕТНОГО БЕЛЬЯ 400 Г</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -3617,7 +3102,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>BLACK ДЛЯ ЧЕРНОГО БЕЛЬЯ 400 Г</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК АВТОМАТ BLACK ДЛЯ ЧЕРНОГО БЕЛЬЯ 400 Г</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -3639,7 +3124,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LEMON ДЛЯ ЦВЕТНОГО БЕЛЬЯ 400 Г</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК АВТОМАТ LEMON ДЛЯ ЦВЕТНОГО БЕЛЬЯ 400 Г</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -3661,7 +3146,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>АРОМАТ РОЗЫ ЦВЕТНОЕ&amp;БЕЛОЕ 400 Г</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК АВТОМАТ АРОМАТ РОЗЫ ЦВЕТНОЕ&amp;БЕЛОЕ 400 Г</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -3683,7 +3168,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>АВТОМАТ 1 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЧЕРНОГО БЕЛЬЯ АВТОМАТ 1 3 КГ</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -3705,7 +3190,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ГОРНЫЙ БРИЗ 1 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ГОРНЫЙ БРИЗ 1 3 КГ</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -3727,7 +3212,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ЛАВАНДА 1 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ЛАВАНДА 1 3 КГ</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -3749,7 +3234,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ПОДСНЕЖНИК 1 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ПОДСНЕЖНИК 1 3 КГ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -3771,7 +3256,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ЛИМОН 1 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ЛИМОН 1 3 КГ</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -3793,7 +3278,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>АВТОМАТ. РОМАШКА 1 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. РОМАШКА 1 3 КГ</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -3815,7 +3300,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>АВТОМАТ.BABY 1 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.BABY 1 3 КГ</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -3837,7 +3322,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>АВТОМАТ.РОЗА 1 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.РОЗА 1 3 КГ</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -3859,7 +3344,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>АВТОМАТ PASSION FRUUT МАРАКУЙЯ 1 5 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЧЕРНОГО БЕЛЬЯ АВТОМАТ PASSION FRUUT МАРАКУЙЯ 1 5 КГ</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -3881,7 +3366,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>АВТОМАТ COLOR 1 5 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ COLOR 1 5 КГ</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -3903,7 +3388,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>АВТОМАТ ROSE РОЗА 1 5 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ ROSE РОЗА 1 5 КГ</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -3925,7 +3410,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>АВТОМАТ PAPATYA РОМАШКА 1 5 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ PAPATYA РОМАШКА 1 5 КГ</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -3947,7 +3432,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>АВТОМАТ LEMON ЛИМОН 1 5 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ LEMON ЛИМОН 1 5 КГ</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -3969,7 +3454,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>АВТОМАТ LAVANDA ЛАВАНДА 1 5 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ LAVANDA ЛАВАНДА 1 5 КГ</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -3991,7 +3476,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>АВТОМАТ ГОРНЫЙ БРИЗ 1 5</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ ГОРНЫЙ БРИЗ 1 5</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4013,7 +3498,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>АВТОМАТ SPRING BREEZE ВЕСЕННИЙ БРИЗ 1 5</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ SPRING BREEZE ВЕСЕННИЙ БРИЗ 1 5</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4035,7 +3520,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>АВТОМАТ MANGO МАНГО 1 5 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ MANGO МАНГО 1 5 КГ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4057,7 +3542,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>АВТОМАТ.РОМАШКА 2 7 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.РОМАШКА 2 7 КГ</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4079,7 +3564,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>АВТОМАТ 2 7 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЧЕРНОГО БЕЛЬЯ АВТОМАТ 2 7 КГ</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -4101,7 +3586,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ГОРНЫЙ БРИЗ 2 7 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ГОРНЫЙ БРИЗ 2 7 КГ</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -4123,7 +3608,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ЛАВАНДА 2 7 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ЛАВАНДА 2 7 КГ</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -4145,7 +3630,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ПОДСНЕЖНИК 2 7 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ПОДСНЕЖНИК 2 7 КГ</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -4167,7 +3652,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ЛИМОН 2 7 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ЛИМОН 2 7 КГ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -4189,7 +3674,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>АВТОМАТ.BABY 2 7 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.BABY 2 7 КГ</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -4211,7 +3696,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>АВТОМАТ.РОЗА 2 7 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.РОЗА 2 7 КГ</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -4233,7 +3718,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>АВТОМАТ. МАНГО 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. МАНГО 3 КГ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -4255,7 +3740,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>АВТОМАТ. ВЕСЕННИЙ БРИЗ 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. ВЕСЕННИЙ БРИЗ 3 КГ</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -4277,7 +3762,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>АВТОМАТ. ГОРНЫЙ БРИЗ 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. ГОРНЫЙ БРИЗ 3 КГ</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -4299,7 +3784,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>АВТОМАТ. ЛАВАНДА 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. ЛАВАНДА 3 КГ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -4321,7 +3806,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>АВТОМАТ. РОМАШКА 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. РОМАШКА 3 КГ</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -4343,7 +3828,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>АВТОМАТ. ЛИМОН 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. ЛИМОН 3 КГ</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -4365,7 +3850,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>АВТОМАТ. РОЗА 3 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. РОЗА 3 КГ</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -4387,7 +3872,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>АВТОМАТ.РОМАШКА 4 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.РОМАШКА 4 КГ</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -4409,7 +3894,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>АВТОМАТ 4 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЧЕРНОГО БЕЛЬЯ АВТОМАТ 4 КГ</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -4431,7 +3916,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ГОРНЫЙ БРИЗ 4 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ГОРНЫЙ БРИЗ 4 КГ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -4453,7 +3938,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ЛАВАНДА 4 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ЛАВАНДА 4 КГ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -4475,7 +3960,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ПОДСНЕЖНИК 4 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ПОДСНЕЖНИК 4 КГ</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -4497,7 +3982,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ЛИМОН 4 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ЛИМОН 4 КГ</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -4519,7 +4004,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>АВТОМАТ.РОЗА 4 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.РОЗА 4 КГ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -4541,7 +4026,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>АВТОМАТ. МАНГО 4 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. МАНГО 4 КГ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -4563,7 +4048,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>АВТОМАТ. COLOR 4 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. COLOR 4 КГ</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -4585,7 +4070,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>АВТОМАТ. МАРАКУЙЯ 4 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. МАРАКУЙЯ 4 КГ</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -4607,7 +4092,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>АВТОМАТ.МАГИНА 5 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.МАГИНА 5 КГ</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -4629,7 +4114,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>АВТОМАТ.РОМАШКА 6 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.РОМАШКА 6 КГ</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -4651,7 +4136,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ГОРНЫЙ БРИЗ 6 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ГОРНЫЙ БРИЗ 6 КГ</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -4673,7 +4158,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ЛАВАНДА 6 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ЛАВАНДА 6 КГ</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -4695,7 +4180,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ПОДСНЕЖНИК 6 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ПОДСНЕЖНИК 6 КГ</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -4717,7 +4202,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ЛИМОН 6 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ЛИМОН 6 КГ</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -4739,7 +4224,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ВЕСЕННИЙ БРИЗ 6 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ВЕСЕННИЙ БРИЗ 6 КГ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -4761,7 +4246,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>АВТОМАТ.МАНГО 6 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.МАНГО 6 КГ</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -4783,7 +4268,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>АВТОМАТ.МАРАКУЙЯ 6 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.МАРАКУЙЯ 6 КГ</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -4805,7 +4290,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>АВТОМАТ.РОЗА 6 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.РОЗА 6 КГ</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -4827,7 +4312,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ПОДСНЕЖНИК 9 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ПОДСНЕЖНИК 9 КГ</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -4849,7 +4334,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ЛАВАНДА 9 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ЛАВАНДА 9 КГ</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -4871,7 +4356,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>АВТОМАТ.РОЗА 9 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.РОЗА 9 КГ</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -4893,7 +4378,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ЛИМОН 9 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ЛИМОН 9 КГ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -4915,7 +4400,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ГОРНЫЙ БРИЗ 9 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ГОРНЫЙ БРИЗ 9 КГ</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -4937,7 +4422,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>АВТОМАТ.РОМАШКА 9 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.РОМАШКА 9 КГ</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -4959,7 +4444,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>АВТОМАТ.ВЕСЕННИЙ БРИЗ 9 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.ВЕСЕННИЙ БРИЗ 9 КГ</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -4981,7 +4466,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>АВТОМАТ.МАРАКУЙЯ 9 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.МАРАКУЙЯ 9 КГ</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -5003,7 +4488,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>АВТОМАТ.МАНГО 9 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.МАНГО 9 КГ</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -5025,7 +4510,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>АВТОМАТ COLOR 9 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ COLOR 9 КГ</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -5047,7 +4532,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>АВТОМАТ.МАНГО 10 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.МАНГО 10 КГ</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -5069,7 +4554,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>АВТОМАТ.МАРАКУЙЯ 10 КГ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ.МАРАКУЙЯ 10 КГ</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -5091,7 +4576,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>АВТОМАТ. 10 КГ ЛАВАНДА</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. 10 КГ ЛАВАНДА</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -5113,7 +4598,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>АВТОМАТ. 10 КГ ЛИМОН</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. 10 КГ ЛИМОН</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -5135,7 +4620,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>АВТОМАТ. 10 КГ РОМАШКА</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. 10 КГ РОМАШКА</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -5157,7 +4642,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>АВТОМАТ. 10 КГ ГОРНЫЙ БРИЗ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. 10 КГ ГОРНЫЙ БРИЗ</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -5179,7 +4664,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>АВТОМАТ. 10 КГ COLOR</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. 10 КГ COLOR</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -5201,7 +4686,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>АВТОМАТ. 10 КГ РОЗА</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. 10 КГ РОЗА</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -5223,7 +4708,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>АВТОМАТ. 10 КГ ВЕСЕННИЙ БРИЗ</t>
+          <t>СТИРАЛЬНЫЙ ПОРОШОК ДЛЯ ЦВЕТНОГО БЕЛЬЯ АВТОМАТ. 10 КГ ВЕСЕННИЙ БРИЗ</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -5243,19 +4728,14 @@
           <t>BOSSFIX</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>SKU-082</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>ЖМС BOSSFIX Baby 1 л</t>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ПОДГУЗНИКИ ОДНОРАЗОВЫЕ (РАЗМЕРЫ 1-2-3-4-5-6)</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5270,19 +4750,14 @@
           <t>BOSSFIX</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>SKU-082</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>ЖМС BOSSFIX Baby 1 л</t>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ВЛАЖНЫЕ ДЕТСКИЕ САЛФЕТКИ (90 ШТ)</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5304,12 +4779,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ MAGINA АРАБСКИЙ ПАРФЮМ 1</t>
+          <t>MAGINA АРАБСКИЙ ПАРФЮМ 1</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -5336,27 +4811,17 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ VELVET 1</t>
+          <t>VELVET 1</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>SKU-027</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Velvet 1 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5378,12 +4843,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ ЛОТОС 1</t>
+          <t>ЛОТОС 1</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -5410,12 +4875,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ МАНГО 1</t>
+          <t>МАНГО 1</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -5442,27 +4907,17 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ DREAM 1</t>
+          <t>DREAM 1</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>SKU-030</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Dream 1 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5484,27 +4939,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ MIDNIGHT 1</t>
+          <t>MIDNIGHT 1</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>SKU-026</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Midnight 1 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5526,27 +4971,17 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ TUTKULU DOHLIA СТРАСТИ 1</t>
+          <t>TUTKULU DOHLIA СТРАСТИ 1</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>SKU-039</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Tutkulu Dahlia 1,44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5568,27 +5003,17 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ PAPATYE РОМАШКА 1</t>
+          <t>PAPATYE РОМАШКА 1</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>SKU-040</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Papatya 1,44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5610,27 +5035,17 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ FLORAL MIST 1</t>
+          <t>FLORAL MIST 1</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>SKU-028</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Floral Mist 1 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5652,27 +5067,17 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ PASSION FRUIT МАРАКУЙЯ 1</t>
+          <t>PASSION FRUIT МАРАКУЙЯ 1</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>SKU-042</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Passion Fruit 1,44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5694,27 +5099,17 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ ORCHIDE ОРХИДЕЯ 1</t>
+          <t>ORCHIDE ОРХИДЕЯ 1</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>SKU-043</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Orchide 1,44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5736,27 +5131,17 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ SAFFRAN ШАФРАН 1</t>
+          <t>SAFFRAN ШАФРАН 1</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>SKU-032</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Saffran 1 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5778,27 +5163,17 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ SHAIK ШЕЙХ 1</t>
+          <t>SHAIK ШЕЙХ 1</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>SKU-045</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Shaik 1,44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5820,27 +5195,17 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ JASMIN ЖАСМИН 1</t>
+          <t>JASMIN ЖАСМИН 1</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>SKU-046</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Jasmin 1,44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5862,22 +5227,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ ROMANTIK ROSE РОМАНТИЧНАЯ РОЗА 1 44</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>SKU-047</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Romantik Rose 1,44 л</t>
+          <t>ROMANTIK ROSE РОМАНТИЧНАЯ РОЗА 1 44</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5899,27 +5254,17 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ SWEET TROPIC 1</t>
+          <t>SWEET TROPIC 1</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>SKU-029</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Sweet Tropic 1 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -5941,12 +5286,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ ROSE РОЗА 1</t>
+          <t>ROSE РОЗА 1</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -5973,12 +5318,12 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>BOTANIC ПАРФЮМИРОВАННЫЙ СЕНТЯБРЬСКОЕ СОЛНЦЕ 1</t>
+          <t>BOTANIC СЕНТЯБРЬСКОЕ СОЛНЦЕ 1</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -6005,12 +5350,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>BOTANIC ПАРФЮМИРОВАННЫЙ ДОЖДЛИВЫЙ АПРЕЛЬ 1</t>
+          <t>BOTANIC ДОЖДЛИВЫЙ АПРЕЛЬ 1</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -6037,27 +5382,17 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ BLACKBERRY ЕЖЕВИКА 1</t>
+          <t>BLACKBERRY ЕЖЕВИКА 1</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>44 л</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>SKU-052</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Blackberry 1,44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6079,12 +5414,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ BABY ДЕТСКИЙ 1</t>
+          <t>BABY ДЕТСКИЙ 1</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -6116,7 +5451,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>44 л</t>
+          <t>44 Л</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -6138,27 +5473,17 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ELEGANT WHITE ДЛЯ БЕЛОГО БЕЛЬЯ 1</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT WHITE ДЛЯ БЕЛОГО БЕЛЬЯ 1</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>SKU-073</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Love Is 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6175,27 +5500,17 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ MANGO 1</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ MANGO 1</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>SKU-072</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Maiden Tower 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6212,27 +5527,17 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ FLORAL MIST 1</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ FLORAL MIST 1</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>SKU-073</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Love Is 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6249,27 +5554,17 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ MIDNIGHT 1</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ MIDNIGHT 1</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>SKU-072</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Maiden Tower 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6286,27 +5581,17 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ SPRING 1</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ SPRING 1</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>SKU-073</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Love Is 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6323,27 +5608,17 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ SWEET TROPIC 1</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ SWEET TROPIC 1</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>SKU-072</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Maiden Tower 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6360,27 +5635,17 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ DREAM 1</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ DREAM 1</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>SKU-069</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Frezya 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6397,27 +5662,17 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ VELVET 1</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT ДЛЯ ЦВЕТНОГО БЕЛЬЯ VELVET 1</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>SKU-073</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Love Is 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6434,27 +5689,17 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ELEGANT BOSSFIX 1</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT 1</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>SKU-073</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Love Is 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6471,27 +5716,17 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ELEGANT BLACK ДЛЯ ЧЕРНОГО БЕЛЬЯ 1</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ELEGANT BLACK ДЛЯ ЧЕРНОГО БЕЛЬЯ 1</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>SKU-068</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Ask 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6508,27 +5743,17 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>BABY ДЛЯ ДЕТСКОГО БЕЛЬЯ 1</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО BABY ДЛЯ ДЕТСКОГО БЕЛЬЯ 1</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>SKU-072</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Maiden Tower 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6545,27 +5770,17 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ДЛЯ ЦВЕТНОГО БЕЛЬЯ ПОЛНОЧЬ MIDNIGHT</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ДЛЯ ЦВЕТНОГО БЕЛЬЯ ПОЛНОЧЬ MIDNIGHT</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>3 л</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>SKU-094</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>ЖМС SVO Midnight 3 л</t>
+          <t>3 Л</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6582,27 +5797,17 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ДЛЯ ЦВЕТНОГО БЕЛЬЯ МЕЧТА DREAM</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ДЛЯ ЦВЕТНОГО БЕЛЬЯ МЕЧТА DREAM</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>3 л</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>SKU-095</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>ЖМС SVO Dream 3 л</t>
+          <t>3 Л</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6619,27 +5824,17 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ДЛЯ ЦВЕТНОГО БЕЛЬЯ БАРХАТ VELVET</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ДЛЯ ЦВЕТНОГО БЕЛЬЯ БАРХАТ VELVET</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>3 л</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>SKU-096</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>ЖМС SVO Velvet 3 л</t>
+          <t>3 Л</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6656,12 +5851,12 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ДЛЯ БЕЛОГО БЕЛЬЯ АНТИ-ПЯТНА</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ДЛЯ БЕЛОГО БЕЛЬЯ АНТИ-ПЯТНА</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>3 л</t>
+          <t>3 Л</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -6683,27 +5878,17 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ДЛЯ ЧЕРНОГО БЕЛЬЯ BLACK</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ДЛЯ ЧЕРНОГО БЕЛЬЯ BLACK</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>3 л</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>SKU-098</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>ЖМС SVO Black 3 л</t>
+          <t>3 Л</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6720,27 +5905,17 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ДЛЯ ЦВЕТНОГО БЕЛЬЯ COLOR</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ДЛЯ ЦВЕТНОГО БЕЛЬЯ COLOR</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>3 л</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>SKU-099</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>ЖМС SVO Color 3 л</t>
+          <t>3 Л</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6757,27 +5932,17 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ДЛЯ БЕЛОГО БЕЛЬЯ WHITE</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ДЛЯ БЕЛОГО БЕЛЬЯ WHITE</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>3 л</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>SKU-100</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>ЖМС SVO White 3 л</t>
+          <t>3 Л</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6794,12 +5959,12 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ДЛЯ ДЕТСКОГО БЕЛЬЯ</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ДЛЯ ДЕТСКОГО БЕЛЬЯ</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>3 л</t>
+          <t>3 Л</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -6821,12 +5986,12 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ДЛЯ ЦВЕТНОГО БЕЛЬЯ ГОРНАЯ СВЕЖЕСТЬ</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ДЛЯ ЦВЕТНОГО БЕЛЬЯ ГОРНАЯ СВЕЖЕСТЬ</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>3 л</t>
+          <t>3 Л</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -6848,12 +6013,12 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ДЛЯ ЦВЕТНОГО БЕЛЬЯ ВЕСЕННЯЯ СВЕЖЕСТЬ</t>
+          <t>ЖИДКОЕ МОЮЩЕЕ СРЕДСТВО ДЛЯ ЦВЕТНОГО БЕЛЬЯ ВЕСЕННЯЯ СВЕЖЕСТЬ</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>3 л</t>
+          <t>3 Л</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -6868,11 +6033,6 @@
           <t>Шампунь органический GILAR с аргановым маслом Argan Oil 500 мл</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C219" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -6880,27 +6040,17 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>С АРГАНОВЫМ МАСЛОМ ARGAN OIL</t>
+          <t>ОРГАНИЧЕСКИЙ С АРГАНОВЫМ МАСЛОМ ARGAN OIL</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>SKU-020</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Шампунь органический GILAR Argan Oil 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6910,11 +6060,6 @@
           <t>Шампунь органический GILAR кофейный Coffee 500 мл</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C220" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -6922,27 +6067,17 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>КОФЕЙНЫЙ COFFEE</t>
+          <t>ОРГАНИЧЕСКИЙ КОФЕЙНЫЙ COFFEE</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>SKU-021</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Шампунь органический GILAR Coffee 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6952,11 +6087,6 @@
           <t>Шампунь органический GILAR с маслом имбиря Ginger Oil 500 мл</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C221" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -6964,27 +6094,17 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>С МАСЛОМ ИМБИРЯ GINGER OIL</t>
+          <t>ОРГАНИЧЕСКИЙ С МАСЛОМ ИМБИРЯ GINGER OIL</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>SKU-022</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Шампунь органический GILAR Ginger 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -6994,11 +6114,6 @@
           <t>Шампунь органический GILAR с лавандовым маслом Lavander Oil 500 мл</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C222" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -7006,27 +6121,17 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>С ЛАВАНДОВЫМ МАСЛОМ LAVANDER OIL</t>
+          <t>ОРГАНИЧЕСКИЙ С ЛАВАНДОВЫМ МАСЛОМ LAVANDER OIL</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>SKU-023</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Шампунь органический GILAR Lavender 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7036,11 +6141,6 @@
           <t>Шампунь органический GILAR с маслом женьшеня  Ginseng Oil 500 мл</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Шампунь</t>
-        </is>
-      </c>
       <c r="C223" t="inlineStr">
         <is>
           <t>GILAR</t>
@@ -7048,27 +6148,17 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>С МАСЛОМ ЖЕНЬШЕНЯ GINSENG OIL</t>
+          <t>ОРГАНИЧЕСКИЙ С МАСЛОМ ЖЕНЬШЕНЯ GINSENG OIL</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>SKU-024</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Шампунь органический GILAR Ginseng 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7085,27 +6175,17 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ORANGE (АПЕЛЬСИН)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ ORANGE (АПЕЛЬСИН)</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>SKU-261</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Orange 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7122,27 +6202,17 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>POMEGRANATE (ГРАНАТ)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ POMEGRANATE (ГРАНАТ)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>SKU-262</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Pomegranate 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7159,27 +6229,17 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>WILDBERRIES (ДИКАЯ ЯГОДА)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ WILDBERRIES (ДИКАЯ ЯГОДА)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>SKU-263</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Wild Berries 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7196,27 +6256,17 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>GINGER (ИМБИРЬ)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ GINGER (ИМБИРЬ)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>SKU-264</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Ginger 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7233,27 +6283,17 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>STRAWBERRY (КЛУБНИКА)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ STRAWBERRY (КЛУБНИКА)</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>SKU-265</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Strawberry 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7270,27 +6310,17 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LEMON (ЛИМОН)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ LEMON (ЛИМОН)</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>SKU-266</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Lemon 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7307,27 +6337,17 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>MANGO (МАНГО)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ MANGO (МАНГО)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>SKU-267</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Mango 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7344,27 +6364,17 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>PASSION (МАРАКУЙЯ)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ PASSION (МАРАКУЙЯ)</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>SKU-268</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Passion 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7381,27 +6391,17 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>APPLE (ЯБЛОКО)</t>
+          <t>МОЮЩЕЕ СРЕДСТВО ДЛЯ МЫТЬЯ ПОСУДЫ APPLE (ЯБЛОКО)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>SKU-269</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>Посуда моющее ср-во SVO Apple 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7423,27 +6423,17 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ ASK ЛЮБОВЬ</t>
+          <t>ASK ЛЮБОВЬ</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>SKU-068</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Ask 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7465,27 +6455,17 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ FREZYA ИРИС</t>
+          <t>FREZYA ИРИС</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>SKU-069</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Frezya 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7507,27 +6487,17 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ GUL РОЗА</t>
+          <t>GUL РОЗА</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>SKU-070</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Gul 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7549,27 +6519,17 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ HUZUR УСПОКАИВАЮЩИЙ</t>
+          <t>HUZUR УСПОКАИВАЮЩИЙ</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>SKU-071</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Huzur 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7591,27 +6551,17 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ MAIDEN TOWER ОРХИДЕЯ</t>
+          <t>MAIDEN TOWER ОРХИДЕЯ</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>SKU-072</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Maiden Tower 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7633,27 +6583,17 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ПАРФЮМИРОВАННЫЙ LOVE IS ЦВЕТОЧНЫЙ</t>
+          <t>LOVE IS ЦВЕТОЧНЫЙ</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>5 л</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>SKU-073</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Love Is 5 л</t>
+          <t>5 Л</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7706,12 +6646,12 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>С МАСЛОМ АЛОЭ ВЕРА</t>
+          <t>ЖИДКОЕ МЫЛО НАТУРАЛЬНОЕ С МАСЛОМ АЛОЭ ВЕРА</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -7733,12 +6673,12 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>С МАСЛОМ ЖЕНЬШЕНЯ</t>
+          <t>ЖИДКОЕ МЫЛО НАТУРАЛЬНОЕ С МАСЛОМ ЖЕНЬШЕНЯ</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -7760,27 +6700,17 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>С МАСЛОМ</t>
+          <t>ЖИДКОЕ МЫЛО НАТУРАЛЬНОЕ С МАСЛОМ</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>500 мл</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>SKU-020</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>Шампунь органический GILAR Argan Oil 500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -7797,12 +6727,12 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>С МАСЛОМ АРГАНЫ</t>
+          <t>ЖИДКОЕ МЫЛО НАТУРАЛЬНОЕ С МАСЛОМ АРГАНЫ</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -7824,12 +6754,12 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>С МАСЛОМ ИМБИРЯ</t>
+          <t>ЖИДКОЕ МЫЛО НАТУРАЛЬНОЕ С МАСЛОМ ИМБИРЯ</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -7851,12 +6781,12 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>С МАСЛОМ МИНДАЛЯ</t>
+          <t>ЖИДКОЕ МЫЛО НАТУРАЛЬНОЕ С МАСЛОМ МИНДАЛЯ</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -7878,12 +6808,12 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>С МАСЛОМ ОРЕХА</t>
+          <t>ЖИДКОЕ МЫЛО НАТУРАЛЬНОЕ С МАСЛОМ ОРЕХА</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -7905,12 +6835,12 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>С ХЛОПКОВЫМ МОЛОКОМ</t>
+          <t>ЖИДКОЕ МЫЛО НАТУРАЛЬНОЕ С ХЛОПКОВЫМ МОЛОКОМ</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -7932,12 +6862,12 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>ЦВЕТОК КАКТУСА</t>
+          <t>ЖИДКОЕ МЫЛО НАТУРАЛЬНОЕ ЦВЕТОК КАКТУСА</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -7959,12 +6889,12 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ШОКОЛАД</t>
+          <t>ЖИДКОЕ МЫЛО НАТУРАЛЬНОЕ ШОКОЛАД</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>500 мл</t>
+          <t>500 МЛ</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -7986,7 +6916,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2Х48 Г ЛИМОН</t>
+          <t>БЛОК ТУАЛЕТНЫЙ ДЛЯ УНИТАЗА 2Х48 Г ЛИМОН</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -8008,7 +6938,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2Х48 Г ОКЕАН</t>
+          <t>БЛОК ТУАЛЕТНЫЙ ДЛЯ УНИТАЗА 2Х48 Г ОКЕАН</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -8030,7 +6960,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2Х48 Г ХВОЯ</t>
+          <t>БЛОК ТУАЛЕТНЫЙ ДЛЯ УНИТАЗА 2Х48 Г ХВОЯ</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -8052,7 +6982,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2Х48 Г ЦВЕТЫ</t>
+          <t>БЛОК ТУАЛЕТНЫЙ ДЛЯ УНИТАЗА 2Х48 Г ЦВЕТЫ</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -8074,7 +7004,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>48 Г ЛИМОН</t>
+          <t>БЛОК ТУАЛЕТНЫЙ ДЛЯ УНИТАЗА 48 Г ЛИМОН</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -8096,7 +7026,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>48 Г ОКЕАН</t>
+          <t>БЛОК ТУАЛЕТНЫЙ ДЛЯ УНИТАЗА 48 Г ОКЕАН</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -8118,7 +7048,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>48 Г ХВОЯ</t>
+          <t>БЛОК ТУАЛЕТНЫЙ ДЛЯ УНИТАЗА 48 Г ХВОЯ</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -8140,7 +7070,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>48 Г ЦВЕТЫ</t>
+          <t>БЛОК ТУАЛЕТНЫЙ ДЛЯ УНИТАЗА 48 Г ЦВЕТЫ</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -8167,27 +7097,17 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>АРОМАТ СТРАСТИ TUTKULU DOHLIA 3 В 1 2</t>
+          <t>++ПАРФЮМ АРОМАТ СТРАСТИ TUTKULU DOHLIA 3 В 1 2</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>7 л</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>SKU-039</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Tutkulu Dahlia 1,44 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -8209,27 +7129,17 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>ЛАВАНДА LAVANDA 3 В 1 2</t>
+          <t>++ПАРФЮМ ЛАВАНДА LAVANDA 3 В 1 2</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>7 л</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>SKU-059</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Lavender 2,7 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -8251,22 +7161,12 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>РОМАНТИЧЕСКИЙ АРОМАТ ROMANTIK GUL 3В1</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>SKU-047</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Romantik Rose 1,44 л</t>
+          <t>++ПАРФЮМ РОМАНТИЧЕСКИЙ АРОМАТ ROMANTIK GUL 3В1</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -8288,27 +7188,17 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ЦВЕТОЧНЫЙ ТУМАН FLORAL MIST 3 В 1 2</t>
+          <t>++ПАРФЮМ ЦВЕТОЧНЫЙ ТУМАН FLORAL MIST 3 В 1 2</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>7 л</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>SKU-028</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Floral Mist 1 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -8330,27 +7220,17 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>ДЛЯ ЧЕРНОГО БЕЛЬЯ BLACK 3 В 1 2</t>
+          <t>++ПАРФЮМ ДЛЯ ЧЕРНОГО БЕЛЬЯ BLACK 3 В 1 2</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>7 л</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>SKU-067</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Black Gel 2,7 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -8372,27 +7252,17 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>АРОМАТ МГНОВЕНИЯ MIDNIGHT 3 В 1 2</t>
+          <t>++ПАРФЮМ АРОМАТ МГНОВЕНИЯ MIDNIGHT 3 В 1 2</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>7 л</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>SKU-026</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Midnight 1 л</t>
+          <t>7 Л</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -8404,22 +7274,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>SKU-025</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Baby 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
@@ -8431,22 +7291,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>1 л</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>SKU-025</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>Кондиционер SVO Baby 1 л</t>
+          <t>1 Л</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
